--- a/Лаба 2.1.xlsx
+++ b/Лаба 2.1.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivankosarev/Documents/ВУЗ/Программная инженерия/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993CB7DD-99FF-804D-A98D-393246FB6200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD911B7-58F7-FB4E-8B76-79E1E6921CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="58">
   <si>
     <t>#</t>
   </si>
@@ -191,6 +204,9 @@
   </si>
   <si>
     <t>32</t>
+  </si>
+  <si>
+    <t>ОР</t>
   </si>
 </sst>
 </file>
@@ -576,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" customWidth="1"/>
@@ -588,9 +604,10 @@
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
     <col min="8" max="8" width="23.83203125" customWidth="1"/>
     <col min="9" max="9" width="23.5" customWidth="1"/>
+    <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,8 +635,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -647,8 +667,12 @@
       <c r="I2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" t="str">
+        <f>IF(AND(B2="Заполнено корректно",C2="Заполнено корректно",E2="Заполнено корректно",I2="Заполнено корректно",OR(F2="М",F2="Ж"),H2="Заполнено корректно"),"Регистрация пользователя","Пользователь не заригестрирован")</f>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -676,8 +700,12 @@
       <c r="I3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J33" si="0">IF(AND(B3="Заполнено корректно",C3="Заполнено корректно",E3="Заполнено корректно",I3="Заполнено корректно",OR(F3="М",F3="Ж"),H3="Заполнено корректно"),"Регистрация пользователя","Пользователь не заригестрирован")</f>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -705,8 +733,12 @@
       <c r="I4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -734,8 +766,12 @@
       <c r="I5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -763,8 +799,12 @@
       <c r="I6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -792,8 +832,12 @@
       <c r="I7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -821,8 +865,12 @@
       <c r="I8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -850,8 +898,12 @@
       <c r="I9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -879,8 +931,12 @@
       <c r="I10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -908,8 +964,12 @@
       <c r="I11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -937,8 +997,12 @@
       <c r="I12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -966,8 +1030,12 @@
       <c r="I13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -995,8 +1063,12 @@
       <c r="I14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1024,8 +1096,12 @@
       <c r="I15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1053,8 +1129,12 @@
       <c r="I16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1082,8 +1162,12 @@
       <c r="I17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -1111,8 +1195,12 @@
       <c r="I18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1140,8 +1228,12 @@
       <c r="I19" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1169,8 +1261,12 @@
       <c r="I20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1198,8 +1294,12 @@
       <c r="I21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1227,8 +1327,12 @@
       <c r="I22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -1256,8 +1360,12 @@
       <c r="I23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1285,8 +1393,12 @@
       <c r="I24" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1314,8 +1426,12 @@
       <c r="I25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1343,8 +1459,12 @@
       <c r="I26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1372,8 +1492,12 @@
       <c r="I27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -1401,8 +1525,12 @@
       <c r="I28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1430,8 +1558,12 @@
       <c r="I29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -1459,8 +1591,12 @@
       <c r="I30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J30" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -1488,8 +1624,12 @@
       <c r="I31" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J31" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -1517,8 +1657,12 @@
       <c r="I32" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J32" t="str">
+        <f t="shared" si="0"/>
+        <v>Регистрация пользователя</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1545,6 +1689,10 @@
       </c>
       <c r="I33" t="s">
         <v>10</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>Пользователь не заригестрирован</v>
       </c>
     </row>
   </sheetData>
